--- a/price.xlsx
+++ b/price.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="104">
   <si>
     <t>盛阳食品城水产类批发价(当日均价、仅供参考)</t>
   </si>
   <si>
-    <t>日期:2026.8.8</t>
+    <t>日期:2026.10.8</t>
   </si>
   <si>
     <t>杂鱼类、淡水鱼类批发价格:</t>
@@ -53,286 +53,277 @@
     <t>鳜鱼(桂鱼)</t>
   </si>
   <si>
+    <t>25-30</t>
+  </si>
+  <si>
+    <t>白鲢</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>10-14.5</t>
+  </si>
+  <si>
+    <t>草鱼</t>
+  </si>
+  <si>
+    <t>7.5-8.5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>花鲢</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>非洲鲫鱼</t>
+  </si>
+  <si>
+    <t>8.5-9</t>
+  </si>
+  <si>
+    <t>鳊鱼</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>红鱼</t>
+  </si>
+  <si>
+    <t>青鱼</t>
+  </si>
+  <si>
+    <t>8.5-10.5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>鲳鱼</t>
+  </si>
+  <si>
+    <t>杂货类批发价格:</t>
+  </si>
+  <si>
+    <t>黄鳝(养殖)</t>
+  </si>
+  <si>
+    <t>35-54</t>
+  </si>
+  <si>
+    <t>银鱼</t>
+  </si>
+  <si>
+    <t>27-31</t>
+  </si>
+  <si>
+    <t>甲鱼(养殖)</t>
+  </si>
+  <si>
+    <t>20-58</t>
+  </si>
+  <si>
+    <t>海银鱼</t>
+  </si>
+  <si>
+    <t>牛蛙(养殖)</t>
+  </si>
+  <si>
+    <t>7.7-8.6</t>
+  </si>
+  <si>
+    <t>河鳗(养殖)</t>
+  </si>
+  <si>
+    <t>26-35</t>
+  </si>
+  <si>
+    <t>泥鳅(养殖)</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <t>蛳螺(养殖)</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>鮰鱼</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>黑鱼</t>
+  </si>
+  <si>
+    <t>8.5-11.5</t>
+  </si>
+  <si>
+    <t>昂刺鱼</t>
+  </si>
+  <si>
+    <t>10-15</t>
+  </si>
+  <si>
+    <t>清江鱼</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>梭子蟹(大中小)</t>
+  </si>
+  <si>
+    <t>虾类批发价格:</t>
+  </si>
+  <si>
+    <t>河虾(100头)</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>基围虾(大中小)</t>
+  </si>
+  <si>
+    <t>23-21-17</t>
+  </si>
+  <si>
+    <t>河虾(130头)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>白虾(大中小)</t>
+  </si>
+  <si>
+    <t>52-35</t>
+  </si>
+  <si>
+    <t>河虾(150头)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>罗氏虾(大中小)</t>
+  </si>
+  <si>
+    <t>40-34-23</t>
+  </si>
+  <si>
+    <t>河虾(160头)</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>斑节虾</t>
+  </si>
+  <si>
+    <t>河虾(180头)</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>黑虎虾</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>螃蟹类批发价格:</t>
+  </si>
+  <si>
+    <t>公 蟹</t>
+  </si>
+  <si>
+    <t>母 蟹</t>
+  </si>
+  <si>
+    <t>规格(两)</t>
+  </si>
+  <si>
+    <t>20-25</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>30-35</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>36-40</t>
+  </si>
+  <si>
+    <t>35-40</t>
+  </si>
+  <si>
+    <t>40-45</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>45-50</t>
+  </si>
+  <si>
+    <t>50-55</t>
+  </si>
+  <si>
     <t>55-60</t>
   </si>
   <si>
-    <t>白鲢</t>
-  </si>
-  <si>
-    <t>3.5-4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>鲈鱼</t>
-  </si>
-  <si>
-    <t>10-15</t>
-  </si>
-  <si>
-    <t>草鱼</t>
-  </si>
-  <si>
-    <t>8.5-11</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>鲤鱼</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>花鲢</t>
-  </si>
-  <si>
-    <t>7.5-8.5</t>
-  </si>
-  <si>
-    <t>非洲鲫鱼</t>
-  </si>
-  <si>
-    <t>8.5-9</t>
-  </si>
-  <si>
-    <t>鳊鱼</t>
-  </si>
-  <si>
-    <t>9.5-11.5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>红鱼</t>
-  </si>
-  <si>
-    <t>青鱼</t>
-  </si>
-  <si>
-    <t>9.5-11</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>鲳鱼</t>
-  </si>
-  <si>
-    <t>杂货类批发价格:</t>
-  </si>
-  <si>
-    <t>黄鳝(养殖)</t>
-  </si>
-  <si>
-    <t>35-46</t>
-  </si>
-  <si>
-    <t>银鱼</t>
-  </si>
-  <si>
-    <t>27-31</t>
-  </si>
-  <si>
-    <t>甲鱼(养殖)</t>
-  </si>
-  <si>
-    <t>20-56</t>
-  </si>
-  <si>
-    <t>海银鱼</t>
-  </si>
-  <si>
-    <t>牛蛙(养殖)</t>
-  </si>
-  <si>
-    <t>6.3-7</t>
-  </si>
-  <si>
-    <t>河鳗(养殖)</t>
-  </si>
-  <si>
-    <t>28-35</t>
-  </si>
-  <si>
-    <t>泥鳅(养殖)</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <t>蛳螺(养殖)</t>
-  </si>
-  <si>
-    <t>3-6</t>
-  </si>
-  <si>
-    <t>鮰鱼</t>
-  </si>
-  <si>
-    <t>鲶鱼</t>
-  </si>
-  <si>
-    <t>黑鱼</t>
-  </si>
-  <si>
-    <t>7.5-9.5</t>
-  </si>
-  <si>
-    <t>昂刺鱼</t>
-  </si>
-  <si>
-    <t>清江鱼</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
-    <t>梭子蟹(大中小)</t>
-  </si>
-  <si>
-    <t>虾类批发价格:</t>
-  </si>
-  <si>
-    <t>河虾(100头)</t>
-  </si>
-  <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>基围虾(大中小)</t>
-  </si>
-  <si>
-    <t>18-17-14</t>
-  </si>
-  <si>
-    <t>河虾(130头)</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>白虾(大中小)</t>
-  </si>
-  <si>
-    <t>60-52</t>
-  </si>
-  <si>
-    <t>河虾(150头)</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>罗氏虾(大中小)</t>
-  </si>
-  <si>
-    <t>37-30-24</t>
-  </si>
-  <si>
-    <t>河虾(160头)</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>斑节虾</t>
-  </si>
-  <si>
-    <t>河虾(180头)</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>黑虎虾</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>螃蟹类批发价格:</t>
-  </si>
-  <si>
-    <t>公</t>
-  </si>
-  <si>
-    <t>蟹</t>
-  </si>
-  <si>
-    <t>母</t>
-  </si>
-  <si>
-    <t>规格(两)</t>
-  </si>
-  <si>
-    <t>26-38</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>18-27</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>35-50</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>45-65</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
     <t>2.8</t>
   </si>
   <si>
+    <t>60-65</t>
+  </si>
+  <si>
     <t>4.5</t>
   </si>
   <si>
+    <t>65-70</t>
+  </si>
+  <si>
+    <t>65-75</t>
+  </si>
+  <si>
+    <t>75-85</t>
+  </si>
+  <si>
     <t>3.5-3.9</t>
   </si>
   <si>
-    <t>龙虾类批发价格:</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>龙虾</t>
-  </si>
-  <si>
-    <t>7-9青</t>
-  </si>
-  <si>
-    <t>22-25</t>
-  </si>
-  <si>
-    <t>7-9红</t>
-  </si>
-  <si>
-    <t>4-6青</t>
-  </si>
-  <si>
-    <t>15-17</t>
-  </si>
-  <si>
-    <t>4-6红</t>
-  </si>
-  <si>
-    <t>3-5</t>
-  </si>
-  <si>
-    <t>12-14</t>
+    <t>80-100</t>
   </si>
 </sst>
 </file>
@@ -340,88 +331,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="187">
+  <fonts count="172">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
-    </font>
-    <font>
-      <name val="报宋"/>
-      <sz val="10.0"/>
-      <color rgb="0A0A0A"/>
     </font>
     <font>
       <name val="报宋"/>
@@ -1489,7 +1405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -2001,283 +1917,157 @@
     <xf numFmtId="0" fontId="131" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="138" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="143" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="15" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="14" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyAlignment="true" applyBorder="true">
@@ -2290,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.9296875" customWidth="true" bestFit="true"/>
@@ -2301,7 +2091,7 @@
     <col min="6" max="6" width="9.48046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="true">
+    <row r="1" ht="16.0" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2111,7 @@
       <c r="E2" s="11"/>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" ht="14.0" customHeight="true">
+    <row r="3" ht="10.0" customHeight="true">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -2351,7 +2141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="10.0" customHeight="true">
+    <row r="5" ht="14.0" customHeight="true">
       <c r="A5" s="25" t="s">
         <v>6</v>
       </c>
@@ -2391,7 +2181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="14.0" customHeight="true">
+    <row r="7" ht="10.0" customHeight="true">
       <c r="A7" s="37" t="s">
         <v>16</v>
       </c>
@@ -2428,12 +2218,12 @@
         <v>24</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="10.0" customHeight="true">
       <c r="A9" s="49" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="50" t="s">
         <v>26</v>
@@ -2442,50 +2232,50 @@
         <v>27</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9" s="53" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="14.0" customHeight="true">
       <c r="A10" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>31</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="60" t="s">
+    </row>
+    <row r="11" ht="10.0" customHeight="true">
+      <c r="A11" s="61" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="11" ht="14.0" customHeight="true">
-      <c r="A11" s="61" t="s">
-        <v>34</v>
       </c>
       <c r="B11" s="62"/>
       <c r="C11" s="63"/>
       <c r="D11" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="65" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="65" t="s">
-        <v>35</v>
       </c>
       <c r="F11" s="66"/>
     </row>
     <row r="12" ht="14.0" customHeight="true">
       <c r="A12" s="67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="68"/>
       <c r="C12" s="69"/>
@@ -2513,24 +2303,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="14.0" customHeight="true">
+    <row r="14" ht="10.0" customHeight="true">
       <c r="A14" s="79" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="80" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="81" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="82" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="84" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="84" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" ht="14.0" customHeight="true">
@@ -2538,100 +2328,100 @@
         <v>11</v>
       </c>
       <c r="B15" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="90"/>
     </row>
-    <row r="16" ht="10.0" customHeight="true">
+    <row r="16" ht="14.0" customHeight="true">
       <c r="A16" s="91" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="93" t="s">
-        <v>45</v>
       </c>
       <c r="D16" s="94" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="96" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" ht="14.0" customHeight="true">
+    </row>
+    <row r="17" ht="10.0" customHeight="true">
       <c r="A17" s="97" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="99" t="s">
         <v>48</v>
-      </c>
-      <c r="C17" s="99" t="s">
-        <v>49</v>
       </c>
       <c r="D17" s="100" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="102" t="s">
+    </row>
+    <row r="18" ht="14.0" customHeight="true">
+      <c r="A18" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="104" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="18" ht="10.0" customHeight="true">
-      <c r="A18" s="103" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="104" t="s">
-        <v>52</v>
       </c>
       <c r="C18" s="105"/>
       <c r="D18" s="106" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E18" s="107" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="14.0" customHeight="true">
       <c r="A19" s="109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="110" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="D19" s="112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="112" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="113" t="s">
+      <c r="F19" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" ht="14.0" customHeight="true">
+    </row>
+    <row r="20" ht="10.0" customHeight="true">
       <c r="A20" s="115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="116" t="s">
         <v>57</v>
@@ -2655,7 +2445,7 @@
       <c r="E21" s="125"/>
       <c r="F21" s="126"/>
     </row>
-    <row r="22" ht="10.0" customHeight="true">
+    <row r="22" ht="14.0" customHeight="true">
       <c r="A22" s="127" t="s">
         <v>3</v>
       </c>
@@ -2755,7 +2545,7 @@
     </row>
     <row r="27" ht="10.0" customHeight="true">
       <c r="A27" s="157" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27" s="158" t="s">
         <v>76</v>
@@ -2764,7 +2554,7 @@
         <v>77</v>
       </c>
       <c r="D27" s="160" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E27" s="161" t="s">
         <v>78</v>
@@ -2790,27 +2580,23 @@
       <c r="B29" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="171" t="s">
+      <c r="C29" s="171"/>
+      <c r="D29" s="172" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="172" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>82</v>
-      </c>
+      <c r="E29" s="173"/>
       <c r="F29" s="174"/>
     </row>
     <row r="30" ht="10.0" customHeight="true">
       <c r="A30" s="175"/>
       <c r="B30" s="176" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="177" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="178" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="179" t="s">
         <v>5</v>
@@ -2825,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="183" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="184" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="E31" s="185" t="s">
         <v>86</v>
-      </c>
-      <c r="E31" s="185" t="s">
-        <v>87</v>
       </c>
       <c r="F31" s="186"/>
     </row>
@@ -2840,15 +2626,17 @@
         <v>11</v>
       </c>
       <c r="B32" s="188" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="190" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="189" t="s">
+      <c r="E32" s="191" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="190" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="191"/>
       <c r="F32" s="192"/>
     </row>
     <row r="33" ht="14.0" customHeight="true">
@@ -2859,12 +2647,14 @@
         <v>16</v>
       </c>
       <c r="C33" s="195" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="196" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="197"/>
+      <c r="E33" s="197" t="s">
+        <v>91</v>
+      </c>
       <c r="F33" s="198"/>
     </row>
     <row r="34" ht="14.0" customHeight="true">
@@ -2874,167 +2664,81 @@
       <c r="B34" s="200" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="201"/>
+      <c r="C34" s="201" t="s">
+        <v>93</v>
+      </c>
       <c r="D34" s="202" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="203"/>
+        <v>87</v>
+      </c>
+      <c r="E34" s="203" t="s">
+        <v>94</v>
+      </c>
       <c r="F34" s="204"/>
     </row>
     <row r="35" ht="14.0" customHeight="true">
       <c r="A35" s="205" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B35" s="206" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="207"/>
+      <c r="C35" s="207" t="s">
+        <v>95</v>
+      </c>
       <c r="D35" s="208" t="s">
-        <v>93</v>
-      </c>
-      <c r="E35" s="209"/>
+        <v>96</v>
+      </c>
+      <c r="E35" s="209" t="s">
+        <v>97</v>
+      </c>
       <c r="F35" s="210"/>
     </row>
-    <row r="36" ht="14.0" customHeight="true">
+    <row r="36" ht="10.0" customHeight="true">
       <c r="A36" s="211" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="212" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="213"/>
+        <v>98</v>
+      </c>
+      <c r="C36" s="213" t="s">
+        <v>99</v>
+      </c>
       <c r="D36" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="215"/>
+      <c r="E36" s="215" t="s">
+        <v>100</v>
+      </c>
       <c r="F36" s="216"/>
     </row>
-    <row r="37" ht="14.0" customHeight="true">
+    <row r="37" ht="10.0" customHeight="true">
       <c r="A37" s="217" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="218" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="219"/>
+        <v>25</v>
+      </c>
+      <c r="C37" s="219" t="s">
+        <v>101</v>
+      </c>
       <c r="D37" s="220" t="s">
-        <v>95</v>
-      </c>
-      <c r="E37" s="221"/>
+        <v>102</v>
+      </c>
+      <c r="E37" s="221" t="s">
+        <v>103</v>
+      </c>
       <c r="F37" s="222"/>
     </row>
-    <row r="38" ht="10.0" customHeight="true">
-      <c r="A38" s="223" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38" s="224"/>
-      <c r="C38" s="225"/>
-      <c r="D38" s="226"/>
-      <c r="E38" s="227"/>
-      <c r="F38" s="228"/>
-    </row>
-    <row r="39" ht="14.0" customHeight="true">
-      <c r="A39" s="229" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="230" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="231" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="232"/>
-      <c r="E39" s="233" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="234"/>
-    </row>
-    <row r="40" ht="14.0" customHeight="true">
-      <c r="A40" s="235" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="236" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="237" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="238"/>
-      <c r="E40" s="239" t="s">
-        <v>100</v>
-      </c>
-      <c r="F40" s="240"/>
-    </row>
-    <row r="41" ht="14.0" customHeight="true">
-      <c r="A41" s="241" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="242" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" s="243" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="244"/>
-      <c r="E41" s="245"/>
-      <c r="F41" s="246"/>
-    </row>
-    <row r="42" ht="10.0" customHeight="true">
-      <c r="A42" s="247" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="248" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="249" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" s="250"/>
-      <c r="E42" s="251" t="s">
-        <v>103</v>
-      </c>
-      <c r="F42" s="252"/>
-    </row>
-    <row r="43" ht="14.0" customHeight="true">
-      <c r="A43" s="253" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="254" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="255" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" s="256"/>
-      <c r="E43" s="257"/>
-      <c r="F43" s="258"/>
-    </row>
-    <row r="44" ht="11.0" customHeight="true">
-      <c r="A44" s="259" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="260" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="261" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="262"/>
-      <c r="E44" s="263" t="s">
-        <v>106</v>
-      </c>
-      <c r="F44" s="264"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="265"/>
-      <c r="B45" s="265"/>
-      <c r="C45" s="265"/>
-      <c r="D45" s="265"/>
-      <c r="E45" s="265"/>
-      <c r="F45" s="265"/>
+    <row r="38">
+      <c r="A38" s="223"/>
+      <c r="B38" s="223"/>
+      <c r="C38" s="223"/>
+      <c r="D38" s="223"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="18">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
@@ -3042,6 +2746,8 @@
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="E32:F32"/>
@@ -3051,13 +2757,6 @@
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
